--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/CONNECTICUT_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/CONNECTICUT_2014.xlsx
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C143">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C149">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C405">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C422">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C675">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C708">
